--- a/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
+++ b/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mandyskchan\Documents\Proposal\Hang Lung\Monthly report\Sep report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_02\HangLung_Amoy_Plaza_and_Fashion_Walk_LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4460996B-645D-48AC-945E-9AB52ED0D26B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0E8D2B-9C77-45F7-9A28-3E974388D7CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hang Lung Sep Report" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
   <si>
     <t>Advertiser :</t>
   </si>
@@ -159,6 +159,66 @@
   </si>
   <si>
     <t xml:space="preserve">                 Official Account</t>
+  </si>
+  <si>
+    <t>千海水產海鮮火鍋放題</t>
+  </si>
+  <si>
+    <t>SuperNormal</t>
+  </si>
+  <si>
+    <t>九份飽</t>
+  </si>
+  <si>
+    <t>泰Cool</t>
+  </si>
+  <si>
+    <t>火火雞肉</t>
+  </si>
+  <si>
+    <t>Casa Cucina</t>
+  </si>
+  <si>
+    <t>Calle Ocho</t>
+  </si>
+  <si>
+    <t>Mercury Recalls by Lost Stars</t>
+  </si>
+  <si>
+    <t>교자상</t>
+  </si>
+  <si>
+    <t>Flat Iron Steak</t>
+  </si>
+  <si>
+    <t>Mini Queen 瑩</t>
+  </si>
+  <si>
+    <t>松植屋</t>
+  </si>
+  <si>
+    <t>24/7 FITNESS</t>
+  </si>
+  <si>
+    <t>歡迎自提淘大店</t>
+  </si>
+  <si>
+    <t>香港置業</t>
+  </si>
+  <si>
+    <t>CANVAS</t>
+  </si>
+  <si>
+    <t>Base8 hair &amp; nail</t>
+  </si>
+  <si>
+    <t>四洲食品體驗館</t>
+  </si>
+  <si>
+    <t>per FACE AESTHEYTIC</t>
+  </si>
+  <si>
+    <t>HOKA</t>
   </si>
 </sst>
 </file>
@@ -169,7 +229,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +444,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202020"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="38">
@@ -824,7 +890,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -932,18 +998,42 @@
     <xf numFmtId="0" fontId="16" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -953,30 +1043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1863,24 +1930,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5060C-2839-4CD0-9F3F-195E810AD0DC}">
   <dimension ref="A1:Y83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.453125" customWidth="1"/>
-    <col min="2" max="2" width="19.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" customWidth="1"/>
-    <col min="5" max="6" width="17.54296875" customWidth="1"/>
-    <col min="7" max="7" width="3.1796875" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" customWidth="1"/>
-    <col min="9" max="14" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="5" max="6" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="14" width="17.5703125" customWidth="1"/>
     <col min="15" max="15" width="5" customWidth="1"/>
-    <col min="16" max="16" width="16.453125" customWidth="1"/>
-    <col min="17" max="18" width="12.453125" customWidth="1"/>
-    <col min="19" max="19" width="23.453125" customWidth="1"/>
-    <col min="20" max="20" width="13.6328125" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" customWidth="1"/>
+    <col min="17" max="18" width="12.42578125" customWidth="1"/>
+    <col min="19" max="19" width="23.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1890,7 +1957,7 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:25" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1900,7 +1967,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1910,22 +1977,22 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="T5" s="19"/>
     </row>
-    <row r="6" spans="1:25" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>42</v>
       </c>
       <c r="T6" s="20"/>
     </row>
-    <row r="7" spans="1:25" s="13" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
@@ -1967,15 +2034,25 @@
       </c>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="25">
+        <v>53567</v>
+      </c>
+      <c r="C8" s="26">
+        <v>16608</v>
+      </c>
+      <c r="D8" s="25">
+        <v>14320</v>
+      </c>
+      <c r="E8" s="26">
+        <v>120744</v>
+      </c>
+      <c r="F8" s="27">
+        <v>8174</v>
+      </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17" t="s">
         <v>21</v>
@@ -1988,15 +2065,25 @@
       <c r="N8" s="18"/>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="28"/>
+      <c r="B9" s="26">
+        <v>41152</v>
+      </c>
+      <c r="C9" s="26">
+        <v>23983</v>
+      </c>
+      <c r="D9" s="26">
+        <v>22684</v>
+      </c>
+      <c r="E9" s="26">
+        <v>116079</v>
+      </c>
+      <c r="F9" s="28">
+        <v>12046</v>
+      </c>
       <c r="G9" s="18"/>
       <c r="H9" s="17" t="s">
         <v>22</v>
@@ -2009,11 +2096,11 @@
       <c r="N9" s="18"/>
       <c r="O9" s="6"/>
     </row>
-    <row r="10" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="1:25" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="46" t="s">
+    <row r="11" spans="1:25" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="35" t="s">
@@ -2035,18 +2122,22 @@
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="47"/>
-      <c r="B12" s="36"/>
+    <row r="12" spans="1:25" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="52"/>
+      <c r="B12" s="36" t="s">
+        <v>45</v>
+      </c>
       <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="33" t="s">
+        <v>55</v>
+      </c>
       <c r="E12"/>
       <c r="F12" s="10"/>
       <c r="G12"/>
-      <c r="H12"/>
+      <c r="H12" s="60"/>
       <c r="I12"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
       <c r="N12" s="10"/>
@@ -2055,11 +2146,16 @@
       <c r="Q12"/>
       <c r="R12"/>
     </row>
-    <row r="13" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="47"/>
-      <c r="B13" s="36"/>
+    <row r="13" spans="1:25" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="52"/>
+      <c r="B13" s="36" t="s">
+        <v>46</v>
+      </c>
       <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="60"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
@@ -2068,29 +2164,37 @@
       <c r="P13" s="22"/>
       <c r="Q13" s="21"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="47"/>
-      <c r="B14" s="36"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="59"/>
+      <c r="Y13" s="59"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="36" t="s">
+        <v>47</v>
+      </c>
       <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="33" t="s">
+        <v>57</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="P14" s="23"/>
       <c r="Q14" s="21"/>
       <c r="R14" s="9"/>
     </row>
-    <row r="15" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="47"/>
-      <c r="B15" s="36"/>
+    <row r="15" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="36" t="s">
+        <v>48</v>
+      </c>
       <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="33" t="s">
+        <v>58</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -2107,16 +2211,20 @@
       <c r="R15" s="9"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="48"/>
-      <c r="B16" s="36"/>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="53"/>
+      <c r="B16" s="36" t="s">
+        <v>49</v>
+      </c>
       <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
+      <c r="D16" s="33" t="s">
+        <v>59</v>
+      </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="T16" s="19"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -2124,8 +2232,8 @@
       <c r="R17" s="9"/>
       <c r="T17" s="19"/>
     </row>
-    <row r="18" spans="1:20" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="46" t="s">
+    <row r="18" spans="1:20" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="51" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="35" t="s">
@@ -2153,31 +2261,43 @@
       <c r="R18" s="9"/>
       <c r="T18" s="19"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A19" s="47"/>
-      <c r="B19" s="36"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="36" t="s">
+        <v>50</v>
+      </c>
       <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
+      <c r="D19" s="33" t="s">
+        <v>60</v>
+      </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="T19" s="19"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A20" s="47"/>
-      <c r="B20" s="36"/>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="36" t="s">
+        <v>51</v>
+      </c>
       <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
+      <c r="D20" s="33" t="s">
+        <v>61</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="T20" s="20"/>
     </row>
-    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="47"/>
-      <c r="B21" s="36"/>
+    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="36" t="s">
+        <v>52</v>
+      </c>
       <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
+      <c r="D21" s="33" t="s">
+        <v>62</v>
+      </c>
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
@@ -2195,23 +2315,31 @@
       <c r="S21"/>
       <c r="T21" s="19"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A22" s="47"/>
-      <c r="B22" s="36"/>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="36" t="s">
+        <v>53</v>
+      </c>
       <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
+      <c r="D22" s="33" t="s">
+        <v>63</v>
+      </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A23" s="48"/>
-      <c r="B23" s="36"/>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="53"/>
+      <c r="B23" s="36" t="s">
+        <v>54</v>
+      </c>
       <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
+      <c r="D23" s="33" t="s">
+        <v>64</v>
+      </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
         <v>7</v>
       </c>
@@ -2228,80 +2356,102 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="55" t="s">
+    <row r="27" spans="1:20" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="52" t="s">
+      <c r="B27" s="15">
+        <v>7377910</v>
+      </c>
+      <c r="C27" s="15">
+        <v>4523</v>
+      </c>
+      <c r="D27" s="45" t="s">
         <v>40</v>
       </c>
       <c r="E27" s="15"/>
     </row>
-    <row r="28" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="56" t="s">
+    <row r="28" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="52" t="s">
+      <c r="B28" s="15">
+        <v>4959925</v>
+      </c>
+      <c r="C28" s="15">
+        <v>3902</v>
+      </c>
+      <c r="D28" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
+      <c r="B29" s="15">
+        <v>6090968</v>
+      </c>
+      <c r="C29" s="15">
+        <v>3973</v>
+      </c>
       <c r="D29" s="44" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="15"/>
     </row>
-    <row r="30" spans="1:20" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="55" t="s">
+    <row r="30" spans="1:20" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="53" t="s">
+      <c r="B30" s="15">
+        <v>6918405</v>
+      </c>
+      <c r="C30" s="15">
+        <v>4238</v>
+      </c>
+      <c r="D30" s="46" t="s">
         <v>32</v>
       </c>
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
+      <c r="B31" s="15">
+        <v>3329028</v>
+      </c>
+      <c r="C31" s="15">
+        <v>2272</v>
+      </c>
       <c r="D31" s="44" t="s">
         <v>37</v>
       </c>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="57"/>
+    <row r="32" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="49"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="15"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A35" s="58" t="s">
+      <c r="E32" s="15">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="58"/>
-      <c r="D35" s="59" t="s">
+      <c r="B35" s="55"/>
+      <c r="D35" s="50" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F36" s="54" t="s">
         <v>36</v>
       </c>
@@ -2312,19 +2462,19 @@
       </c>
       <c r="K36" s="54"/>
     </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F83" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="W13:Y13"/>
     <mergeCell ref="A18:A23"/>
     <mergeCell ref="A11:A16"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="J12:K12"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="W13:Y13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
+++ b/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_02\HangLung_Amoy_Plaza_and_Fashion_Walk_LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0E8D2B-9C77-45F7-9A28-3E974388D7CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6443FD-72F5-44C0-853C-90F64554A96B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2369,7 +2369,9 @@
       <c r="D27" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="15"/>
+      <c r="E27" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
@@ -2384,7 +2386,9 @@
       <c r="D28" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="15"/>
+      <c r="E28" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="29" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
@@ -2399,7 +2403,9 @@
       <c r="D29" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="15"/>
+      <c r="E29" s="15">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:20" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="47" t="s">
@@ -2414,7 +2420,9 @@
       <c r="D30" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="15"/>
+      <c r="E30" s="15">
+        <v>11</v>
+      </c>
     </row>
     <row r="31" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
@@ -2429,7 +2437,9 @@
       <c r="D31" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="15"/>
+      <c r="E31" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="32" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
@@ -2439,7 +2449,7 @@
         <v>34</v>
       </c>
       <c r="E32" s="15">
-        <v>3973</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">

--- a/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
+++ b/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_02\HangLung_Amoy_Plaza_and_Fashion_Walk_LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6443FD-72F5-44C0-853C-90F64554A96B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB8DE2B-A759-4776-A05A-AD724299A12B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
   <si>
     <t>Advertiser :</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>HOKA</t>
+  </si>
+  <si>
+    <t>牛気</t>
+  </si>
+  <si>
+    <t>阿城鵝肉</t>
+  </si>
+  <si>
+    <t>鮨政</t>
   </si>
 </sst>
 </file>
@@ -890,7 +899,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1044,6 +1053,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="36" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1095,9 +1105,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF99FF"/>
       <color rgb="FF0000FF"/>
       <color rgb="FFFF66CC"/>
-      <color rgb="FFFF99FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2057,12 +2067,24 @@
       <c r="H8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
+      <c r="I8" s="16">
+        <v>914</v>
+      </c>
+      <c r="J8" s="18">
+        <v>5</v>
+      </c>
+      <c r="K8" s="18">
+        <v>622</v>
+      </c>
+      <c r="L8" s="18">
+        <v>18</v>
+      </c>
+      <c r="M8" s="18">
+        <v>20</v>
+      </c>
+      <c r="N8" s="18">
+        <v>1562</v>
+      </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2088,12 +2110,24 @@
       <c r="H9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
+      <c r="I9" s="18">
+        <v>2377</v>
+      </c>
+      <c r="J9" s="18">
+        <v>12</v>
+      </c>
+      <c r="K9" s="18">
+        <v>4083</v>
+      </c>
+      <c r="L9" s="18">
+        <v>4</v>
+      </c>
+      <c r="M9" s="18">
+        <v>5</v>
+      </c>
+      <c r="N9" s="61">
+        <v>2317</v>
+      </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -2127,7 +2161,9 @@
       <c r="B12" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="33"/>
+      <c r="C12" s="33" t="s">
+        <v>46</v>
+      </c>
       <c r="D12" s="33" t="s">
         <v>55</v>
       </c>
@@ -2151,7 +2187,9 @@
       <c r="B13" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="33" t="s">
+        <v>65</v>
+      </c>
       <c r="D13" s="33" t="s">
         <v>56</v>
       </c>
@@ -2176,7 +2214,9 @@
       <c r="B14" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="33"/>
+      <c r="C14" s="33" t="s">
+        <v>66</v>
+      </c>
       <c r="D14" s="33" t="s">
         <v>57</v>
       </c>
@@ -2266,7 +2306,9 @@
       <c r="B19" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="33"/>
+      <c r="C19" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="D19" s="33" t="s">
         <v>60</v>
       </c>
@@ -2279,7 +2321,9 @@
       <c r="B20" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="33"/>
+      <c r="C20" s="33" t="s">
+        <v>50</v>
+      </c>
       <c r="D20" s="33" t="s">
         <v>61</v>
       </c>
@@ -2294,7 +2338,9 @@
       <c r="B21" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="33"/>
+      <c r="C21" s="33" t="s">
+        <v>53</v>
+      </c>
       <c r="D21" s="33" t="s">
         <v>62</v>
       </c>
@@ -2320,7 +2366,9 @@
       <c r="B22" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="33"/>
+      <c r="C22" s="33" t="s">
+        <v>54</v>
+      </c>
       <c r="D22" s="33" t="s">
         <v>63</v>
       </c>
@@ -2332,7 +2380,9 @@
       <c r="B23" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="33"/>
+      <c r="C23" s="33" t="s">
+        <v>67</v>
+      </c>
       <c r="D23" s="33" t="s">
         <v>64</v>
       </c>

--- a/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
+++ b/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_02\HangLung_Amoy_Plaza_and_Fashion_Walk_LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB8DE2B-A759-4776-A05A-AD724299A12B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037F6CB6-7BDD-4C75-8C28-F12758349840}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t>Advertiser :</t>
   </si>
@@ -228,6 +228,15 @@
   </si>
   <si>
     <t>鮨政</t>
+  </si>
+  <si>
+    <t>FeatureItemId</t>
+  </si>
+  <si>
+    <t>ClickId</t>
+  </si>
+  <si>
+    <t>CampaignId</t>
   </si>
 </sst>
 </file>
@@ -238,7 +247,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,6 +468,19 @@
       <color rgb="FF202020"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="38">
@@ -899,7 +921,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1025,6 +1047,17 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="36" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1043,17 +1076,18 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="36" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1192,8 +1226,8 @@
       <xdr:rowOff>119945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>435822</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>954405</xdr:colOff>
       <xdr:row>72</xdr:row>
       <xdr:rowOff>70557</xdr:rowOff>
     </xdr:to>
@@ -1947,7 +1981,7 @@
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.85546875" customWidth="1"/>
     <col min="5" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="8" max="8" width="16.42578125" customWidth="1"/>
     <col min="9" max="14" width="17.5703125" customWidth="1"/>
     <col min="15" max="15" width="5" customWidth="1"/>
@@ -2125,7 +2159,7 @@
       <c r="M9" s="18">
         <v>5</v>
       </c>
-      <c r="N9" s="61">
+      <c r="N9" s="52">
         <v>2317</v>
       </c>
       <c r="O9" s="6"/>
@@ -2134,7 +2168,7 @@
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:25" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="56" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="35" t="s">
@@ -2157,7 +2191,7 @@
       <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:25" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="52"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="36" t="s">
         <v>45</v>
       </c>
@@ -2170,10 +2204,10 @@
       <c r="E12"/>
       <c r="F12" s="10"/>
       <c r="G12"/>
-      <c r="H12" s="60"/>
+      <c r="H12" s="51"/>
       <c r="I12"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
       <c r="N12" s="10"/>
@@ -2183,7 +2217,7 @@
       <c r="R12"/>
     </row>
     <row r="13" spans="1:25" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
+      <c r="A13" s="57"/>
       <c r="B13" s="36" t="s">
         <v>46</v>
       </c>
@@ -2193,7 +2227,7 @@
       <c r="D13" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="51"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
@@ -2202,15 +2236,15 @@
       <c r="P13" s="22"/>
       <c r="Q13" s="21"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="57"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="59"/>
-      <c r="Y13" s="59"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="W13" s="53"/>
+      <c r="X13" s="55"/>
+      <c r="Y13" s="55"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="57"/>
       <c r="B14" s="36" t="s">
         <v>47</v>
       </c>
@@ -2227,7 +2261,7 @@
       <c r="R14" s="9"/>
     </row>
     <row r="15" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="57"/>
       <c r="B15" s="36" t="s">
         <v>48</v>
       </c>
@@ -2252,7 +2286,7 @@
       <c r="T15" s="19"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="53"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="36" t="s">
         <v>49</v>
       </c>
@@ -2273,7 +2307,7 @@
       <c r="T17" s="19"/>
     </row>
     <row r="18" spans="1:20" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="56" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="35" t="s">
@@ -2302,7 +2336,7 @@
       <c r="T18" s="19"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
+      <c r="A19" s="57"/>
       <c r="B19" s="36" t="s">
         <v>50</v>
       </c>
@@ -2317,7 +2351,7 @@
       <c r="T19" s="19"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="57"/>
       <c r="B20" s="36" t="s">
         <v>51</v>
       </c>
@@ -2334,7 +2368,7 @@
       <c r="T20" s="20"/>
     </row>
     <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="36" t="s">
         <v>52</v>
       </c>
@@ -2362,7 +2396,7 @@
       <c r="T21" s="19"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="57"/>
       <c r="B22" s="36" t="s">
         <v>53</v>
       </c>
@@ -2376,7 +2410,7 @@
       <c r="R22" s="7"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="36" t="s">
         <v>54</v>
       </c>
@@ -2389,7 +2423,7 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
         <v>7</v>
       </c>
@@ -2404,6 +2438,15 @@
       </c>
       <c r="E26" s="39" t="s">
         <v>8</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="63" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -2422,6 +2465,15 @@
       <c r="E27" s="15">
         <v>4</v>
       </c>
+      <c r="F27" s="64">
+        <v>43016</v>
+      </c>
+      <c r="G27" s="64">
+        <v>7418544476</v>
+      </c>
+      <c r="H27" s="64">
+        <v>214</v>
+      </c>
     </row>
     <row r="28" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
@@ -2439,6 +2491,15 @@
       <c r="E28" s="15">
         <v>7</v>
       </c>
+      <c r="F28" s="64">
+        <v>42986</v>
+      </c>
+      <c r="G28" s="64">
+        <v>7371461683</v>
+      </c>
+      <c r="H28" s="64">
+        <v>211</v>
+      </c>
     </row>
     <row r="29" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
@@ -2456,6 +2517,15 @@
       <c r="E29" s="15">
         <v>15</v>
       </c>
+      <c r="F29" s="64">
+        <v>41971</v>
+      </c>
+      <c r="G29" s="64">
+        <v>7289878736</v>
+      </c>
+      <c r="H29" s="64">
+        <v>209</v>
+      </c>
     </row>
     <row r="30" spans="1:20" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="47" t="s">
@@ -2473,6 +2543,15 @@
       <c r="E30" s="15">
         <v>11</v>
       </c>
+      <c r="F30" s="64">
+        <v>43017</v>
+      </c>
+      <c r="G30" s="64">
+        <v>7418574409</v>
+      </c>
+      <c r="H30" s="64">
+        <v>201</v>
+      </c>
     </row>
     <row r="31" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
@@ -2489,6 +2568,15 @@
       </c>
       <c r="E31" s="15">
         <v>5</v>
+      </c>
+      <c r="F31" s="64">
+        <v>43081</v>
+      </c>
+      <c r="G31" s="64">
+        <v>7433721277</v>
+      </c>
+      <c r="H31" s="64">
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2501,26 +2589,31 @@
       <c r="E32" s="15">
         <v>7</v>
       </c>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="64">
+        <v>182</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="55"/>
+      <c r="B35" s="60"/>
       <c r="D35" s="50" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F36" s="54" t="s">
+      <c r="F36" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="J36" s="54" t="s">
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="J36" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="K36" s="54"/>
+      <c r="K36" s="59"/>
     </row>
     <row r="83" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F83" s="5"/>

--- a/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
+++ b/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/Hang Lung Monthly LMS Report_Sep 1-30,2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_02\HangLung_Amoy_Plaza_and_Fashion_Walk_LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037F6CB6-7BDD-4C75-8C28-F12758349840}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4670FF0-E175-44E1-A639-05BD24772824}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1049,6 +1049,18 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="36" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1075,18 +1087,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2168,7 +2168,7 @@
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:25" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="60" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="35" t="s">
@@ -2191,7 +2191,7 @@
       <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:25" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="36" t="s">
         <v>45</v>
       </c>
@@ -2206,8 +2206,8 @@
       <c r="G12"/>
       <c r="H12" s="51"/>
       <c r="I12"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
       <c r="N12" s="10"/>
@@ -2217,7 +2217,7 @@
       <c r="R12"/>
     </row>
     <row r="13" spans="1:25" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="57"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="36" t="s">
         <v>46</v>
       </c>
@@ -2236,15 +2236,15 @@
       <c r="P13" s="22"/>
       <c r="Q13" s="21"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="55"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="59"/>
+      <c r="Y13" s="59"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="36" t="s">
         <v>47</v>
       </c>
@@ -2261,7 +2261,7 @@
       <c r="R14" s="9"/>
     </row>
     <row r="15" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="36" t="s">
         <v>48</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="T15" s="19"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="36" t="s">
         <v>49</v>
       </c>
@@ -2307,7 +2307,7 @@
       <c r="T17" s="19"/>
     </row>
     <row r="18" spans="1:20" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="60" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="35" t="s">
@@ -2336,7 +2336,7 @@
       <c r="T18" s="19"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="36" t="s">
         <v>50</v>
       </c>
@@ -2351,7 +2351,7 @@
       <c r="T19" s="19"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="57"/>
+      <c r="A20" s="61"/>
       <c r="B20" s="36" t="s">
         <v>51</v>
       </c>
@@ -2368,7 +2368,7 @@
       <c r="T20" s="20"/>
     </row>
     <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="36" t="s">
         <v>52</v>
       </c>
@@ -2396,7 +2396,7 @@
       <c r="T21" s="19"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="57"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="36" t="s">
         <v>53</v>
       </c>
@@ -2410,7 +2410,7 @@
       <c r="R22" s="7"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="58"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="36" t="s">
         <v>54</v>
       </c>
@@ -2439,13 +2439,13 @@
       <c r="E26" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="62" t="s">
+      <c r="F26" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="62" t="s">
+      <c r="G26" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="63" t="s">
+      <c r="H26" s="54" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="E27" s="15">
         <v>4</v>
       </c>
-      <c r="F27" s="64">
+      <c r="F27" s="55">
         <v>43016</v>
       </c>
-      <c r="G27" s="64">
+      <c r="G27" s="55">
         <v>7418544476</v>
       </c>
-      <c r="H27" s="64">
+      <c r="H27" s="55">
         <v>214</v>
       </c>
     </row>
@@ -2491,13 +2491,13 @@
       <c r="E28" s="15">
         <v>7</v>
       </c>
-      <c r="F28" s="64">
+      <c r="F28" s="55">
         <v>42986</v>
       </c>
-      <c r="G28" s="64">
+      <c r="G28" s="55">
         <v>7371461683</v>
       </c>
-      <c r="H28" s="64">
+      <c r="H28" s="55">
         <v>211</v>
       </c>
     </row>
@@ -2517,13 +2517,13 @@
       <c r="E29" s="15">
         <v>15</v>
       </c>
-      <c r="F29" s="64">
+      <c r="F29" s="55">
         <v>41971</v>
       </c>
-      <c r="G29" s="64">
+      <c r="G29" s="55">
         <v>7289878736</v>
       </c>
-      <c r="H29" s="64">
+      <c r="H29" s="55">
         <v>209</v>
       </c>
     </row>
@@ -2543,13 +2543,13 @@
       <c r="E30" s="15">
         <v>11</v>
       </c>
-      <c r="F30" s="64">
+      <c r="F30" s="55">
         <v>43017</v>
       </c>
-      <c r="G30" s="64">
+      <c r="G30" s="55">
         <v>7418574409</v>
       </c>
-      <c r="H30" s="64">
+      <c r="H30" s="55">
         <v>201</v>
       </c>
     </row>
@@ -2569,13 +2569,13 @@
       <c r="E31" s="15">
         <v>5</v>
       </c>
-      <c r="F31" s="64">
+      <c r="F31" s="55">
         <v>43081</v>
       </c>
-      <c r="G31" s="64">
+      <c r="G31" s="55">
         <v>7433721277</v>
       </c>
-      <c r="H31" s="64">
+      <c r="H31" s="55">
         <v>208</v>
       </c>
     </row>
@@ -2589,31 +2589,31 @@
       <c r="E32" s="15">
         <v>7</v>
       </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="64">
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="55">
         <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="60"/>
+      <c r="B35" s="64"/>
       <c r="D35" s="50" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F36" s="59" t="s">
+      <c r="F36" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="J36" s="59" t="s">
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="J36" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="K36" s="59"/>
+      <c r="K36" s="63"/>
     </row>
     <row r="83" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F83" s="5"/>
